--- a/customer_registration_forms/040_fashion_brand_customer_information_form--customer_registration_forms.xlsx
+++ b/customer_registration_forms/040_fashion_brand_customer_information_form--customer_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>customer_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Customer Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,18 +543,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>last_name</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Email Address</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,114 +566,130 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone_number</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Phone Number</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Enter a 10-digit phone number</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>phone_number</t>
+          <t>style_preferences</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Phone Number</t>
+          <t>Style Preferences</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Enter a 10-digit phone number</t>
+          <t>Select from below options</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>style_preferences</t>
+          <t>date_of_birth</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Style Preferences</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Date of Birth</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>YYYY/MM/DD</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>date_of_birth</t>
+          <t>style_preferred_color</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Date of Birth</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Style Preferred Color</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Select from below options</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>style_preferred_color</t>
+          <t>style_preferred_size</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Style Preferred Color</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Style Preferred Size</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Select from below options</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -685,407 +701,101 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>style_preferred_size</t>
+          <t>style_preferred_fit</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Style Preferred Size</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Style Preferred Fit</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Select from below options</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>style_preferred_fit</t>
+          <t>marketing_opt_in</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Style Preferred Fit</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Marketing Opt-in</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Select from below options</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>marketing_opt_in</t>
+          <t>style_preferred_brand</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Marketing Opt-in</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Style Preferred Brand</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Select from below options</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>marketing_opt_out</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Opt-out from Marketing</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Additional Comments</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Enter any additional comments</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>style_preferred_brand</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Style Preferred Brand</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Additional Comments</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Additional Comments</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>style_preferences</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Style Preferences</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>phone_number</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Phone Number</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>date_of_birth</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Date of Birth</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>style_preferred_size</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Style Preferred Size</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>style_preferred_fit</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Style Preferred Fit</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>style_preferred_color</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Style Preferred Color</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>marketing_opt_in</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Marketing Opt-in</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>marketing_opt_out</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Opt-out from Marketing</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>style_preferred_brand</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Style Preferred Brand</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1102,7 +812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -1135,12 +845,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>casual</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Casual</t>
         </is>
       </c>
     </row>
@@ -1152,12 +862,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>formal</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Formal</t>
         </is>
       </c>
     </row>
@@ -1169,29 +879,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>style_preferred_color_choices</t>
+          <t>style_preferences_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>sporty</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Sporty</t>
         </is>
       </c>
     </row>
@@ -1203,12 +913,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -1220,12 +930,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
@@ -1237,29 +947,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yellow</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>style_preferred_size_choices</t>
+          <t>style_preferred_color_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>yellow</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>Yellow</t>
         </is>
       </c>
     </row>
@@ -1271,12 +981,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
@@ -1288,46 +998,46 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>style_preferred_fit_choices</t>
+          <t>style_preferred_size_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>loose</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Loose</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>style_preferred_fit_choices</t>
+          <t>style_preferred_size_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>comfortable</t>
+          <t>xl</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Comfortable</t>
+          <t>XL</t>
         </is>
       </c>
     </row>
@@ -1339,53 +1049,53 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>fitted</t>
+          <t>loose</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fitted</t>
+          <t>Loose</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>marketing_opt_in_choices</t>
+          <t>style_preferred_fit_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>comfortable</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Comfortable</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>marketing_opt_in_choices</t>
+          <t>style_preferred_fit_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>fitted</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Fitted</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>marketing_opt_out_choices</t>
+          <t>marketing_opt_in_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1402,7 +1112,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>marketing_opt_out_choices</t>
+          <t>marketing_opt_in_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1462,329 +1172,6 @@
         </is>
       </c>
       <c r="C21" t="inlineStr">
-        <is>
-          <t>Brand 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>style_preferences_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>style_preferences_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>style_preferences_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>style_preferred_size_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>small</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Small</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>style_preferred_size_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>style_preferred_size_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>large</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Large</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>style_preferred_fit_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>loose</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Loose</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>style_preferred_fit_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>comfortable</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Comfortable</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>style_preferred_fit_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>fitted</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Fitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>style_preferred_color_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>style_preferred_color_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>style_preferred_color_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>marketing_opt_in_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>marketing_opt_in_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>marketing_opt_out_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>marketing_opt_out_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>style_preferred_brand_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>brand_1</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Brand 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>style_preferred_brand_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>brand_2</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Brand 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>style_preferred_brand_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>brand_3</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
         <is>
           <t>Brand 3</t>
         </is>
